--- a/docs/03_detail_design/画面項目定義書.xlsx
+++ b/docs/03_detail_design/画面項目定義書.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kamed\OneDrive\ドキュメント\勤怠アプリ開発\詳細設計\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kamed\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9E09A3D-6DA5-450A-AA8B-60395CD56CAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8FD1F44-ABDC-4FA7-A7CE-0FF0BD04721B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-135" yWindow="-16335" windowWidth="29070" windowHeight="15750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,15 @@
     <sheet name="SCR003_勤怠一覧画面" sheetId="5" r:id="rId5"/>
     <sheet name="SCR004_管理者メニュー" sheetId="6" r:id="rId6"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">表紙!$A$1:$H$20</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="312">
   <si>
     <t>勤怠管理アプリ
 画面項目定義書</t>
@@ -276,10 +279,16 @@
     <t>-</t>
   </si>
   <si>
+    <t>ユーザーID未入力時、パスワード未入力時、認証失敗時に表示</t>
+  </si>
+  <si>
     <t>username/password入力時に押下可</t>
   </si>
   <si>
-    <t>認証処理を実行</t>
+    <t>MSG001, MSG002, MSG003 を表示</t>
+  </si>
+  <si>
+    <t>画面上部に赤字表示</t>
   </si>
   <si>
     <t>エラーメッセージ</t>
@@ -304,9 +313,6 @@
   </si>
   <si>
     <t>認証失敗メッセージを表示</t>
-  </si>
-  <si>
-    <t>画面上部に赤字表示</t>
   </si>
   <si>
     <t>4. 補足事項</t>
@@ -556,7 +562,13 @@
     <t>logoutButton</t>
   </si>
   <si>
-    <t>POST /logout 実行</t>
+    <t>出勤/退勤/休憩開始/休憩終了の処理完了時またはエラー時に表示</t>
+  </si>
+  <si>
+    <t>MSG004～MSG012 を表示</t>
+  </si>
+  <si>
+    <t>画面上部に表示（FlashAttributes）</t>
   </si>
   <si>
     <t>結果メッセージ</t>
@@ -789,16 +801,16 @@
     <t>workDuration</t>
   </si>
   <si>
-    <t>算出可能時に表示</t>
-  </si>
-  <si>
-    <t>退勤済みのみ算出</t>
+    <t>対象月0件時、不正な対象年月指定時、表示形式異常時に表示</t>
+  </si>
+  <si>
+    <t>MSG014, MSG015, MSG016 を表示</t>
   </si>
   <si>
     <t>attendance_records.clock_in_at / clock_out_at</t>
   </si>
   <si>
-    <t>休憩控除後の時間</t>
+    <t>一覧上部に表示</t>
   </si>
   <si>
     <t>データなしメッセージ</t>
@@ -811,9 +823,6 @@
   </si>
   <si>
     <t>対象月の勤怠データはありません。</t>
-  </si>
-  <si>
-    <t>一覧上部に表示</t>
   </si>
   <si>
     <t>ホームへ戻るリンク</t>
@@ -933,6 +942,15 @@
   </si>
   <si>
     <t>csvExportLink</t>
+  </si>
+  <si>
+    <t>一般社員がアクセスした時、未実装機能選択時に表示</t>
+  </si>
+  <si>
+    <t>MSG017, MSG018 を表示</t>
+  </si>
+  <si>
+    <t>権限エラーまたは案内メッセージ</t>
   </si>
   <si>
     <t>案内メッセージ</t>
@@ -1200,10 +1218,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1212,6 +1226,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1231,17 +1249,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1258,6 +1276,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1556,108 +1578,100 @@
     <row r="1" spans="2:8" ht="49.95" customHeight="1"/>
     <row r="2" spans="2:8" ht="49.95" customHeight="1"/>
     <row r="3" spans="2:8" ht="49.95" customHeight="1"/>
-    <row r="4" spans="2:8" ht="25.05" customHeight="1">
-      <c r="B4" s="5" t="s">
+    <row r="4" spans="2:8">
+      <c r="B4" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-    </row>
-    <row r="5" spans="2:8" ht="25.05" customHeight="1">
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-    </row>
-    <row r="6" spans="2:8" ht="25.05" customHeight="1">
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-    </row>
-    <row r="7" spans="2:8" ht="25.05" customHeight="1"/>
-    <row r="8" spans="2:8" ht="25.05" customHeight="1"/>
-    <row r="9" spans="2:8" ht="25.05" customHeight="1"/>
-    <row r="10" spans="2:8" ht="30" customHeight="1">
-      <c r="C10" s="7" t="s">
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+    </row>
+    <row r="5" spans="2:8">
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+    </row>
+    <row r="6" spans="2:8">
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+    </row>
+    <row r="10" spans="2:8">
+      <c r="C10" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="9" t="s">
+      <c r="D10" s="6"/>
+      <c r="E10" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F10" s="10"/>
-      <c r="G10" s="8"/>
-    </row>
-    <row r="11" spans="2:8" ht="25.05" customHeight="1"/>
-    <row r="12" spans="2:8" ht="30" customHeight="1">
-      <c r="C12" s="7" t="s">
+      <c r="F10" s="8"/>
+      <c r="G10" s="6"/>
+    </row>
+    <row r="12" spans="2:8">
+      <c r="C12" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="9" t="s">
+      <c r="D12" s="6"/>
+      <c r="E12" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F12" s="10"/>
-      <c r="G12" s="8"/>
-    </row>
-    <row r="13" spans="2:8" ht="25.05" customHeight="1"/>
-    <row r="14" spans="2:8" ht="30" customHeight="1">
-      <c r="C14" s="7" t="s">
+      <c r="F12" s="8"/>
+      <c r="G12" s="6"/>
+    </row>
+    <row r="14" spans="2:8">
+      <c r="C14" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="9" t="s">
+      <c r="D14" s="6"/>
+      <c r="E14" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F14" s="10"/>
-      <c r="G14" s="8"/>
-    </row>
-    <row r="15" spans="2:8" ht="25.05" customHeight="1"/>
-    <row r="16" spans="2:8" ht="30" customHeight="1">
-      <c r="C16" s="7" t="s">
+      <c r="F14" s="8"/>
+      <c r="G14" s="6"/>
+    </row>
+    <row r="16" spans="2:8">
+      <c r="C16" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="8"/>
-      <c r="E16" s="9" t="s">
+      <c r="D16" s="6"/>
+      <c r="E16" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F16" s="10"/>
-      <c r="G16" s="8"/>
-    </row>
-    <row r="17" spans="3:7" ht="25.05" customHeight="1"/>
-    <row r="18" spans="3:7" ht="30" customHeight="1">
-      <c r="C18" s="7" t="s">
+      <c r="F16" s="8"/>
+      <c r="G16" s="6"/>
+    </row>
+    <row r="18" spans="3:7">
+      <c r="C18" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="8"/>
-      <c r="E18" s="9" t="s">
+      <c r="D18" s="6"/>
+      <c r="E18" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F18" s="10"/>
-      <c r="G18" s="8"/>
-    </row>
-    <row r="19" spans="3:7" ht="25.05" customHeight="1"/>
-    <row r="20" spans="3:7" ht="30" customHeight="1">
-      <c r="C20" s="7" t="s">
+      <c r="F18" s="8"/>
+      <c r="G18" s="6"/>
+    </row>
+    <row r="20" spans="3:7">
+      <c r="C20" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D20" s="8"/>
-      <c r="E20" s="9" t="s">
+      <c r="D20" s="6"/>
+      <c r="E20" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F20" s="10"/>
-      <c r="G20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="6"/>
     </row>
     <row r="21" spans="3:7" ht="25.05" customHeight="1"/>
     <row r="22" spans="3:7" ht="25.05" customHeight="1"/>
@@ -1666,6 +1680,12 @@
     <row r="25" spans="3:7" ht="25.05" customHeight="1"/>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B4:H6"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E16:G16"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="E10:G10"/>
     <mergeCell ref="C12:D12"/>
@@ -1673,12 +1693,6 @@
     <mergeCell ref="E14:G14"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="E20:G20"/>
-    <mergeCell ref="B4:H6"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E16:G16"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1696,50 +1710,49 @@
     <col min="3" max="10" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="21" customHeight="1">
+    <row r="1" spans="1:10">
       <c r="A1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-    </row>
-    <row r="3" spans="1:10" ht="19.95" customHeight="1"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+    </row>
     <row r="4" spans="1:10">
       <c r="A4" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="8"/>
-    </row>
-    <row r="5" spans="1:10" ht="19.95" customHeight="1">
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="6"/>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" s="12" t="s">
         <v>15</v>
       </c>
@@ -1753,19 +1766,19 @@
       <c r="I5" s="13"/>
       <c r="J5" s="14"/>
     </row>
-    <row r="6" spans="1:10" ht="19.95" customHeight="1">
+    <row r="6" spans="1:10">
       <c r="A6" s="15"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
       <c r="J6" s="16"/>
     </row>
-    <row r="7" spans="1:10" ht="19.95" customHeight="1">
+    <row r="7" spans="1:10">
       <c r="A7" s="17"/>
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
@@ -1777,22 +1790,21 @@
       <c r="I7" s="18"/>
       <c r="J7" s="19"/>
     </row>
-    <row r="8" spans="1:10" ht="19.95" customHeight="1"/>
-    <row r="9" spans="1:10" ht="19.95" customHeight="1">
+    <row r="9" spans="1:10">
       <c r="A9" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="8"/>
-    </row>
-    <row r="10" spans="1:10" ht="19.95" customHeight="1">
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="6"/>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" s="12" t="s">
         <v>17</v>
       </c>
@@ -1808,17 +1820,17 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="15"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
       <c r="J11" s="16"/>
     </row>
-    <row r="12" spans="1:10" ht="19.95" customHeight="1">
+    <row r="12" spans="1:10">
       <c r="A12" s="17"/>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
@@ -1830,22 +1842,21 @@
       <c r="I12" s="18"/>
       <c r="J12" s="19"/>
     </row>
-    <row r="13" spans="1:10" ht="19.95" customHeight="1"/>
-    <row r="14" spans="1:10" ht="19.95" customHeight="1">
+    <row r="14" spans="1:10">
       <c r="A14" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="8"/>
-    </row>
-    <row r="15" spans="1:10" ht="64.05" customHeight="1">
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="6"/>
+    </row>
+    <row r="15" spans="1:10" ht="28.2" customHeight="1">
       <c r="A15" s="12" t="s">
         <v>19</v>
       </c>
@@ -1859,19 +1870,19 @@
       <c r="I15" s="13"/>
       <c r="J15" s="14"/>
     </row>
-    <row r="16" spans="1:10" ht="19.95" customHeight="1">
+    <row r="16" spans="1:10" ht="28.2" customHeight="1">
       <c r="A16" s="15"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
       <c r="J16" s="16"/>
     </row>
-    <row r="17" spans="1:10" ht="19.95" customHeight="1">
+    <row r="17" spans="1:10" ht="28.2" customHeight="1">
       <c r="A17" s="17"/>
       <c r="B17" s="18"/>
       <c r="C17" s="18"/>
@@ -1883,22 +1894,21 @@
       <c r="I17" s="18"/>
       <c r="J17" s="19"/>
     </row>
-    <row r="18" spans="1:10" ht="19.95" customHeight="1"/>
-    <row r="19" spans="1:10" ht="19.95" customHeight="1">
+    <row r="19" spans="1:10">
       <c r="A19" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="8"/>
-    </row>
-    <row r="20" spans="1:10" ht="19.95" customHeight="1">
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="6"/>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" s="12" t="s">
         <v>21</v>
       </c>
@@ -1914,17 +1924,17 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="15"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
       <c r="J21" s="16"/>
     </row>
-    <row r="22" spans="1:10" ht="19.95" customHeight="1">
+    <row r="22" spans="1:10">
       <c r="A22" s="17"/>
       <c r="B22" s="18"/>
       <c r="C22" s="18"/>
@@ -1936,22 +1946,21 @@
       <c r="I22" s="18"/>
       <c r="J22" s="19"/>
     </row>
-    <row r="23" spans="1:10" ht="19.95" customHeight="1"/>
-    <row r="24" spans="1:10" ht="19.95" customHeight="1">
+    <row r="24" spans="1:10">
       <c r="A24" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="8"/>
-    </row>
-    <row r="25" spans="1:10" ht="19.95" customHeight="1">
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="6"/>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" s="12" t="s">
         <v>23</v>
       </c>
@@ -1965,19 +1974,19 @@
       <c r="I25" s="13"/>
       <c r="J25" s="14"/>
     </row>
-    <row r="26" spans="1:10" ht="19.95" customHeight="1">
+    <row r="26" spans="1:10">
       <c r="A26" s="15"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="10"/>
       <c r="J26" s="16"/>
     </row>
-    <row r="27" spans="1:10" ht="19.95" customHeight="1">
+    <row r="27" spans="1:10">
       <c r="A27" s="17"/>
       <c r="B27" s="18"/>
       <c r="C27" s="18"/>
@@ -1989,22 +1998,21 @@
       <c r="I27" s="18"/>
       <c r="J27" s="19"/>
     </row>
-    <row r="28" spans="1:10" ht="19.95" customHeight="1"/>
-    <row r="29" spans="1:10" ht="19.95" customHeight="1">
+    <row r="29" spans="1:10">
       <c r="A29" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
-      <c r="I29" s="10"/>
-      <c r="J29" s="8"/>
-    </row>
-    <row r="30" spans="1:10" ht="19.95" customHeight="1">
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="6"/>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" s="12" t="s">
         <v>25</v>
       </c>
@@ -2018,19 +2026,19 @@
       <c r="I30" s="13"/>
       <c r="J30" s="14"/>
     </row>
-    <row r="31" spans="1:10" ht="19.95" customHeight="1">
+    <row r="31" spans="1:10">
       <c r="A31" s="15"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="10"/>
+      <c r="I31" s="10"/>
       <c r="J31" s="16"/>
     </row>
-    <row r="32" spans="1:10" ht="19.95" customHeight="1">
+    <row r="32" spans="1:10">
       <c r="A32" s="17"/>
       <c r="B32" s="18"/>
       <c r="C32" s="18"/>
@@ -2070,176 +2078,174 @@
   <dimension ref="A1:L62"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
-    <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="23" customWidth="1"/>
-    <col min="11" max="11" width="28" customWidth="1"/>
-    <col min="12" max="12" width="26" customWidth="1"/>
+    <col min="3" max="3" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="61.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="36.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="36" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="29.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="30" customHeight="1">
+    <row r="1" spans="1:12">
       <c r="A1" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-    </row>
-    <row r="2" spans="1:12" ht="19.95" customHeight="1">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-    </row>
-    <row r="3" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="4" spans="1:12" ht="24" customHeight="1">
-      <c r="A4" s="22" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="8"/>
-    </row>
-    <row r="5" spans="1:12" ht="19.95" customHeight="1">
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="6"/>
+    </row>
+    <row r="5" spans="1:12" ht="16.2">
       <c r="A5" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="6"/>
       <c r="F5" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="8"/>
-    </row>
-    <row r="6" spans="1:12" ht="19.95" customHeight="1">
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="6"/>
+    </row>
+    <row r="6" spans="1:12" ht="16.2">
       <c r="A6" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="6"/>
       <c r="F6" s="3" t="s">
         <v>35</v>
       </c>
       <c r="G6" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="8"/>
-    </row>
-    <row r="7" spans="1:12" ht="19.95" customHeight="1">
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="6"/>
+    </row>
+    <row r="7" spans="1:12" ht="16.2">
       <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="6"/>
       <c r="F7" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G7" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="8"/>
-    </row>
-    <row r="8" spans="1:12" ht="19.95" customHeight="1">
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="6"/>
+    </row>
+    <row r="8" spans="1:12" ht="16.2">
       <c r="A8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="6"/>
       <c r="F8" s="3" t="s">
         <v>42</v>
       </c>
       <c r="G8" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="8"/>
-    </row>
-    <row r="9" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="10" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="11" spans="1:12" ht="24" customHeight="1">
-      <c r="A11" s="22" t="s">
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="6"/>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="8"/>
-    </row>
-    <row r="12" spans="1:12" ht="79.95" customHeight="1">
-      <c r="A12" s="23" t="s">
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="6"/>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="25" t="s">
         <v>45</v>
       </c>
       <c r="B12" s="13"/>
@@ -2256,105 +2262,105 @@
       <c r="K12" s="13"/>
       <c r="L12" s="14"/>
     </row>
-    <row r="13" spans="1:12" ht="19.95" customHeight="1">
+    <row r="13" spans="1:12">
       <c r="A13" s="15"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
       <c r="E13" s="16"/>
       <c r="F13" s="15"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
       <c r="L13" s="16"/>
     </row>
-    <row r="14" spans="1:12" ht="19.95" customHeight="1">
+    <row r="14" spans="1:12">
       <c r="A14" s="15"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
       <c r="E14" s="16"/>
       <c r="F14" s="15"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
       <c r="L14" s="16"/>
     </row>
-    <row r="15" spans="1:12" ht="19.95" customHeight="1">
+    <row r="15" spans="1:12">
       <c r="A15" s="15"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
       <c r="E15" s="16"/>
       <c r="F15" s="15"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
       <c r="L15" s="16"/>
     </row>
-    <row r="16" spans="1:12" ht="19.95" customHeight="1">
+    <row r="16" spans="1:12">
       <c r="A16" s="15"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
       <c r="E16" s="16"/>
       <c r="F16" s="15"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10"/>
       <c r="L16" s="16"/>
     </row>
-    <row r="17" spans="1:12" ht="19.95" customHeight="1">
+    <row r="17" spans="1:12">
       <c r="A17" s="15"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
       <c r="E17" s="16"/>
       <c r="F17" s="15"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
       <c r="L17" s="16"/>
     </row>
-    <row r="18" spans="1:12" ht="19.95" customHeight="1">
+    <row r="18" spans="1:12">
       <c r="A18" s="15"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
       <c r="E18" s="16"/>
       <c r="F18" s="15"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10"/>
       <c r="L18" s="16"/>
     </row>
-    <row r="19" spans="1:12" ht="19.95" customHeight="1">
+    <row r="19" spans="1:12">
       <c r="A19" s="15"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
       <c r="E19" s="16"/>
       <c r="F19" s="15"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10"/>
       <c r="L19" s="16"/>
     </row>
-    <row r="20" spans="1:12" ht="19.95" customHeight="1">
+    <row r="20" spans="1:12">
       <c r="A20" s="17"/>
       <c r="B20" s="18"/>
       <c r="C20" s="18"/>
@@ -2368,23 +2374,23 @@
       <c r="K20" s="18"/>
       <c r="L20" s="19"/>
     </row>
-    <row r="21" spans="1:12" ht="24" customHeight="1">
-      <c r="A21" s="22" t="s">
+    <row r="21" spans="1:12">
+      <c r="A21" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="8"/>
-    </row>
-    <row r="22" spans="1:12" ht="19.95" customHeight="1">
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="6"/>
+    </row>
+    <row r="22" spans="1:12" ht="16.2">
       <c r="A22" s="4" t="s">
         <v>48</v>
       </c>
@@ -2422,7 +2428,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="19.95" customHeight="1">
+    <row r="23" spans="1:12" ht="16.2">
       <c r="A23" s="1">
         <v>1</v>
       </c>
@@ -2460,7 +2466,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="19.95" customHeight="1">
+    <row r="24" spans="1:12" ht="16.2">
       <c r="A24" s="1">
         <v>2</v>
       </c>
@@ -2498,7 +2504,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="19.95" customHeight="1">
+    <row r="25" spans="1:12" ht="16.2">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -2521,85 +2527,78 @@
         <v>79</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>79</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="19.95" customHeight="1">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="16.2">
       <c r="A26" s="1">
         <v>4</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="L26" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="28" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="29" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="30" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="31" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="32" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="33" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="34" spans="1:12" ht="24" customHeight="1">
-      <c r="A34" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="10"/>
-      <c r="J34" s="10"/>
-      <c r="K34" s="10"/>
-      <c r="L34" s="8"/>
-    </row>
-    <row r="35" spans="1:12" ht="48" customHeight="1">
-      <c r="A35" s="25" t="s">
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34" s="23" t="s">
         <v>92</v>
+      </c>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="6"/>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35" s="24" t="s">
+        <v>93</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -2613,63 +2612,63 @@
       <c r="K35" s="13"/>
       <c r="L35" s="14"/>
     </row>
-    <row r="36" spans="1:12" ht="19.95" customHeight="1">
+    <row r="36" spans="1:12">
       <c r="A36" s="15"/>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="6"/>
-      <c r="J36" s="6"/>
-      <c r="K36" s="6"/>
+      <c r="B36" s="10"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="10"/>
+      <c r="I36" s="10"/>
+      <c r="J36" s="10"/>
+      <c r="K36" s="10"/>
       <c r="L36" s="16"/>
     </row>
-    <row r="37" spans="1:12" ht="19.95" customHeight="1">
+    <row r="37" spans="1:12">
       <c r="A37" s="15"/>
-      <c r="B37" s="6"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6"/>
-      <c r="J37" s="6"/>
-      <c r="K37" s="6"/>
+      <c r="B37" s="10"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="10"/>
+      <c r="I37" s="10"/>
+      <c r="J37" s="10"/>
+      <c r="K37" s="10"/>
       <c r="L37" s="16"/>
     </row>
-    <row r="38" spans="1:12" ht="19.95" customHeight="1">
+    <row r="38" spans="1:12">
       <c r="A38" s="15"/>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="6"/>
-      <c r="K38" s="6"/>
+      <c r="B38" s="10"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="10"/>
+      <c r="G38" s="10"/>
+      <c r="H38" s="10"/>
+      <c r="I38" s="10"/>
+      <c r="J38" s="10"/>
+      <c r="K38" s="10"/>
       <c r="L38" s="16"/>
     </row>
-    <row r="39" spans="1:12" ht="19.95" customHeight="1">
+    <row r="39" spans="1:12">
       <c r="A39" s="15"/>
-      <c r="B39" s="6"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="6"/>
-      <c r="K39" s="6"/>
+      <c r="B39" s="10"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="10"/>
+      <c r="F39" s="10"/>
+      <c r="G39" s="10"/>
+      <c r="H39" s="10"/>
+      <c r="I39" s="10"/>
+      <c r="J39" s="10"/>
+      <c r="K39" s="10"/>
       <c r="L39" s="16"/>
     </row>
-    <row r="40" spans="1:12" ht="19.95" customHeight="1">
+    <row r="40" spans="1:12">
       <c r="A40" s="17"/>
       <c r="B40" s="18"/>
       <c r="C40" s="18"/>
@@ -2683,53 +2682,47 @@
       <c r="K40" s="18"/>
       <c r="L40" s="19"/>
     </row>
-    <row r="41" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="42" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="43" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="44" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="45" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="46" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="47" spans="1:12" ht="24" customHeight="1">
-      <c r="A47" s="22" t="s">
-        <v>93</v>
-      </c>
-      <c r="B47" s="10"/>
-      <c r="C47" s="10"/>
-      <c r="D47" s="10"/>
-      <c r="E47" s="10"/>
-      <c r="F47" s="10"/>
-      <c r="G47" s="10"/>
-      <c r="H47" s="10"/>
-      <c r="I47" s="10"/>
-      <c r="J47" s="10"/>
-      <c r="K47" s="10"/>
-      <c r="L47" s="8"/>
-    </row>
-    <row r="48" spans="1:12" ht="19.95" customHeight="1">
+    <row r="47" spans="1:12">
+      <c r="A47" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="8"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="8"/>
+      <c r="I47" s="8"/>
+      <c r="J47" s="8"/>
+      <c r="K47" s="8"/>
+      <c r="L47" s="6"/>
+    </row>
+    <row r="48" spans="1:12" ht="16.2">
       <c r="A48" s="4" t="s">
         <v>48</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="F48" s="24"/>
-      <c r="G48" s="10"/>
-      <c r="H48" s="10"/>
-      <c r="I48" s="10"/>
-      <c r="J48" s="10"/>
-      <c r="K48" s="10"/>
-      <c r="L48" s="8"/>
-    </row>
-    <row r="49" spans="1:12" ht="19.95" customHeight="1">
+        <v>98</v>
+      </c>
+      <c r="F48" s="22"/>
+      <c r="G48" s="8"/>
+      <c r="H48" s="8"/>
+      <c r="I48" s="8"/>
+      <c r="J48" s="8"/>
+      <c r="K48" s="8"/>
+      <c r="L48" s="6"/>
+    </row>
+    <row r="49" spans="1:12" ht="16.2">
       <c r="A49" s="1">
         <v>1</v>
       </c>
@@ -2737,23 +2730,23 @@
         <v>60</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F49" s="12"/>
-      <c r="G49" s="10"/>
-      <c r="H49" s="10"/>
-      <c r="I49" s="10"/>
-      <c r="J49" s="10"/>
-      <c r="K49" s="10"/>
-      <c r="L49" s="8"/>
-    </row>
-    <row r="50" spans="1:12" ht="19.95" customHeight="1">
+      <c r="G49" s="8"/>
+      <c r="H49" s="8"/>
+      <c r="I49" s="8"/>
+      <c r="J49" s="8"/>
+      <c r="K49" s="8"/>
+      <c r="L49" s="6"/>
+    </row>
+    <row r="50" spans="1:12" ht="16.2">
       <c r="A50" s="1">
         <v>2</v>
       </c>
@@ -2761,28 +2754,28 @@
         <v>71</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F50" s="12"/>
-      <c r="G50" s="10"/>
-      <c r="H50" s="10"/>
-      <c r="I50" s="10"/>
-      <c r="J50" s="10"/>
-      <c r="K50" s="10"/>
-      <c r="L50" s="8"/>
-    </row>
-    <row r="51" spans="1:12" ht="31.95" customHeight="1">
+      <c r="G50" s="8"/>
+      <c r="H50" s="8"/>
+      <c r="I50" s="8"/>
+      <c r="J50" s="8"/>
+      <c r="K50" s="8"/>
+      <c r="L50" s="6"/>
+    </row>
+    <row r="51" spans="1:12" ht="32.4">
       <c r="A51" s="1">
         <v>3</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>79</v>
@@ -2791,123 +2784,106 @@
         <v>79</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F51" s="12"/>
-      <c r="G51" s="10"/>
-      <c r="H51" s="10"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="10"/>
-      <c r="K51" s="10"/>
-      <c r="L51" s="8"/>
-    </row>
-    <row r="52" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="53" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="54" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="55" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="56" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="57" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="58" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="59" spans="1:12" ht="24" customHeight="1">
-      <c r="A59" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="B59" s="10"/>
-      <c r="C59" s="10"/>
-      <c r="D59" s="10"/>
-      <c r="E59" s="10"/>
-      <c r="F59" s="10"/>
-      <c r="G59" s="10"/>
-      <c r="H59" s="10"/>
-      <c r="I59" s="10"/>
-      <c r="J59" s="10"/>
-      <c r="K59" s="10"/>
-      <c r="L59" s="8"/>
-    </row>
-    <row r="60" spans="1:12" ht="19.95" customHeight="1">
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="6"/>
+    </row>
+    <row r="59" spans="1:12">
+      <c r="A59" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="B59" s="8"/>
+      <c r="C59" s="8"/>
+      <c r="D59" s="8"/>
+      <c r="E59" s="8"/>
+      <c r="F59" s="8"/>
+      <c r="G59" s="8"/>
+      <c r="H59" s="8"/>
+      <c r="I59" s="8"/>
+      <c r="J59" s="8"/>
+      <c r="K59" s="8"/>
+      <c r="L59" s="6"/>
+    </row>
+    <row r="60" spans="1:12" ht="16.2">
       <c r="A60" s="4" t="s">
         <v>48</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E60" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F60" s="24"/>
-      <c r="G60" s="10"/>
-      <c r="H60" s="10"/>
-      <c r="I60" s="10"/>
-      <c r="J60" s="10"/>
-      <c r="K60" s="10"/>
-      <c r="L60" s="8"/>
-    </row>
-    <row r="61" spans="1:12" ht="31.95" customHeight="1">
+      <c r="F60" s="22"/>
+      <c r="G60" s="8"/>
+      <c r="H60" s="8"/>
+      <c r="I60" s="8"/>
+      <c r="J60" s="8"/>
+      <c r="K60" s="8"/>
+      <c r="L60" s="6"/>
+    </row>
+    <row r="61" spans="1:12" ht="32.4">
       <c r="A61" s="1">
         <v>1</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F61" s="12"/>
-      <c r="G61" s="10"/>
-      <c r="H61" s="10"/>
-      <c r="I61" s="10"/>
-      <c r="J61" s="10"/>
-      <c r="K61" s="10"/>
-      <c r="L61" s="8"/>
-    </row>
-    <row r="62" spans="1:12" ht="19.95" customHeight="1">
+      <c r="G61" s="8"/>
+      <c r="H61" s="8"/>
+      <c r="I61" s="8"/>
+      <c r="J61" s="8"/>
+      <c r="K61" s="8"/>
+      <c r="L61" s="6"/>
+    </row>
+    <row r="62" spans="1:12" ht="32.4">
       <c r="A62" s="1">
         <v>2</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F62" s="12"/>
-      <c r="G62" s="10"/>
-      <c r="H62" s="10"/>
-      <c r="I62" s="10"/>
-      <c r="J62" s="10"/>
-      <c r="K62" s="10"/>
-      <c r="L62" s="8"/>
+      <c r="G62" s="8"/>
+      <c r="H62" s="8"/>
+      <c r="I62" s="8"/>
+      <c r="J62" s="8"/>
+      <c r="K62" s="8"/>
+      <c r="L62" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="F61:L61"/>
-    <mergeCell ref="F48:L48"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A21:L21"/>
-    <mergeCell ref="A35:L40"/>
-    <mergeCell ref="F60:L60"/>
-    <mergeCell ref="F49:L49"/>
-    <mergeCell ref="F51:L51"/>
-    <mergeCell ref="A59:L59"/>
-    <mergeCell ref="F50:L50"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="G8:L8"/>
     <mergeCell ref="F62:L62"/>
@@ -2924,10 +2900,20 @@
     <mergeCell ref="A12:E20"/>
     <mergeCell ref="G6:L6"/>
     <mergeCell ref="B6:E6"/>
+    <mergeCell ref="F61:L61"/>
+    <mergeCell ref="F48:L48"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="A21:L21"/>
+    <mergeCell ref="A35:L40"/>
+    <mergeCell ref="F60:L60"/>
+    <mergeCell ref="F49:L49"/>
+    <mergeCell ref="F51:L51"/>
+    <mergeCell ref="A59:L59"/>
+    <mergeCell ref="F50:L50"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" scale="43" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="29" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2936,176 +2922,174 @@
   <dimension ref="A1:L63"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
-    <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="23" customWidth="1"/>
-    <col min="11" max="11" width="28" customWidth="1"/>
-    <col min="12" max="12" width="26" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="65.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="29.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="31.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="60" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="30" customHeight="1">
+    <row r="1" spans="1:12">
       <c r="A1" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-    </row>
-    <row r="2" spans="1:12" ht="19.95" customHeight="1">
+        <v>109</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-    </row>
-    <row r="3" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="4" spans="1:12" ht="24" customHeight="1">
-      <c r="A4" s="22" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="8"/>
-    </row>
-    <row r="5" spans="1:12" ht="19.95" customHeight="1">
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="6"/>
+    </row>
+    <row r="5" spans="1:12" ht="16.2">
       <c r="A5" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="8"/>
+        <v>115</v>
+      </c>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="6"/>
       <c r="F5" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="8"/>
-    </row>
-    <row r="6" spans="1:12" ht="19.95" customHeight="1">
+        <v>116</v>
+      </c>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="6"/>
+    </row>
+    <row r="6" spans="1:12" ht="16.2">
       <c r="A6" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="8"/>
+        <v>117</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="6"/>
       <c r="F6" s="3" t="s">
         <v>35</v>
       </c>
       <c r="G6" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="8"/>
-    </row>
-    <row r="7" spans="1:12" ht="19.95" customHeight="1">
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="6"/>
+    </row>
+    <row r="7" spans="1:12" ht="16.2">
       <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="8"/>
+        <v>118</v>
+      </c>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="6"/>
       <c r="F7" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="8"/>
-    </row>
-    <row r="8" spans="1:12" ht="19.95" customHeight="1">
+        <v>119</v>
+      </c>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="6"/>
+    </row>
+    <row r="8" spans="1:12" ht="16.2">
       <c r="A8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="8"/>
+        <v>120</v>
+      </c>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="6"/>
       <c r="F8" s="3" t="s">
         <v>42</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="8"/>
-    </row>
-    <row r="9" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="10" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="11" spans="1:12" ht="24" customHeight="1">
-      <c r="A11" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="6"/>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="8"/>
-    </row>
-    <row r="12" spans="1:12" ht="90" customHeight="1">
-      <c r="A12" s="23" t="s">
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="6"/>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="25" t="s">
         <v>45</v>
       </c>
       <c r="B12" s="13"/>
@@ -3113,7 +3097,7 @@
       <c r="D12" s="13"/>
       <c r="E12" s="14"/>
       <c r="F12" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13"/>
@@ -3122,105 +3106,105 @@
       <c r="K12" s="13"/>
       <c r="L12" s="14"/>
     </row>
-    <row r="13" spans="1:12" ht="19.95" customHeight="1">
+    <row r="13" spans="1:12">
       <c r="A13" s="15"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
       <c r="E13" s="16"/>
       <c r="F13" s="15"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
       <c r="L13" s="16"/>
     </row>
-    <row r="14" spans="1:12" ht="19.95" customHeight="1">
+    <row r="14" spans="1:12">
       <c r="A14" s="15"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
       <c r="E14" s="16"/>
       <c r="F14" s="15"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
       <c r="L14" s="16"/>
     </row>
-    <row r="15" spans="1:12" ht="19.95" customHeight="1">
+    <row r="15" spans="1:12">
       <c r="A15" s="15"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
       <c r="E15" s="16"/>
       <c r="F15" s="15"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
       <c r="L15" s="16"/>
     </row>
-    <row r="16" spans="1:12" ht="19.95" customHeight="1">
+    <row r="16" spans="1:12">
       <c r="A16" s="15"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
       <c r="E16" s="16"/>
       <c r="F16" s="15"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10"/>
       <c r="L16" s="16"/>
     </row>
-    <row r="17" spans="1:12" ht="19.95" customHeight="1">
+    <row r="17" spans="1:12">
       <c r="A17" s="15"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
       <c r="E17" s="16"/>
       <c r="F17" s="15"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
       <c r="L17" s="16"/>
     </row>
-    <row r="18" spans="1:12" ht="19.95" customHeight="1">
+    <row r="18" spans="1:12">
       <c r="A18" s="15"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
       <c r="E18" s="16"/>
       <c r="F18" s="15"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10"/>
       <c r="L18" s="16"/>
     </row>
-    <row r="19" spans="1:12" ht="19.95" customHeight="1">
+    <row r="19" spans="1:12">
       <c r="A19" s="15"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
       <c r="E19" s="16"/>
       <c r="F19" s="15"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10"/>
       <c r="L19" s="16"/>
     </row>
-    <row r="20" spans="1:12" ht="19.95" customHeight="1">
+    <row r="20" spans="1:12">
       <c r="A20" s="17"/>
       <c r="B20" s="18"/>
       <c r="C20" s="18"/>
@@ -3234,23 +3218,23 @@
       <c r="K20" s="18"/>
       <c r="L20" s="19"/>
     </row>
-    <row r="21" spans="1:12" ht="24" customHeight="1">
-      <c r="A21" s="22" t="s">
+    <row r="21" spans="1:12">
+      <c r="A21" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="8"/>
-    </row>
-    <row r="22" spans="1:12" ht="19.95" customHeight="1">
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="6"/>
+    </row>
+    <row r="22" spans="1:12" ht="16.2">
       <c r="A22" s="4" t="s">
         <v>48</v>
       </c>
@@ -3288,15 +3272,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="19.95" customHeight="1">
+    <row r="23" spans="1:12" ht="16.2">
       <c r="A23" s="1">
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>61</v>
@@ -3308,13 +3292,13 @@
         <v>79</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>65</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>79</v>
@@ -3323,94 +3307,94 @@
         <v>68</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="19.95" customHeight="1">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="16.2">
       <c r="A24" s="1">
         <v>2</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>79</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>65</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>79</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="31.95" customHeight="1">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="16.2">
       <c r="A25" s="1">
         <v>3</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>61</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>79</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>65</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="19.95" customHeight="1">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="16.2">
       <c r="A26" s="1">
         <v>4</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>78</v>
@@ -3428,27 +3412,27 @@
         <v>65</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="19.95" customHeight="1">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="16.2">
       <c r="A27" s="1">
         <v>5</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>78</v>
@@ -3466,27 +3450,27 @@
         <v>65</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="19.95" customHeight="1">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="16.2">
       <c r="A28" s="1">
         <v>6</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>78</v>
@@ -3504,27 +3488,27 @@
         <v>65</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="19.95" customHeight="1">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="16.2">
       <c r="A29" s="1">
         <v>7</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>78</v>
@@ -3542,30 +3526,30 @@
         <v>65</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="19.95" customHeight="1">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="16.2">
       <c r="A30" s="1">
         <v>8</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>79</v>
@@ -3580,7 +3564,7 @@
         <v>65</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>79</v>
@@ -3589,18 +3573,18 @@
         <v>79</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="19.95" customHeight="1">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="16.2">
       <c r="A31" s="1">
         <v>9</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>78</v>
@@ -3615,79 +3599,78 @@
         <v>79</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>65</v>
+        <v>172</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>79</v>
+        <v>173</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>79</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" ht="19.95" customHeight="1">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="16.2">
       <c r="A32" s="1">
         <v>10</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>79</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>79</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="34" spans="1:12" ht="24" customHeight="1">
-      <c r="A34" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="10"/>
-      <c r="J34" s="10"/>
-      <c r="K34" s="10"/>
-      <c r="L34" s="8"/>
-    </row>
-    <row r="35" spans="1:12" ht="48" customHeight="1">
-      <c r="A35" s="25" t="s">
-        <v>177</v>
+        <v>179</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="6"/>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35" s="24" t="s">
+        <v>180</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -3701,63 +3684,63 @@
       <c r="K35" s="13"/>
       <c r="L35" s="14"/>
     </row>
-    <row r="36" spans="1:12" ht="19.95" customHeight="1">
+    <row r="36" spans="1:12">
       <c r="A36" s="15"/>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="6"/>
-      <c r="J36" s="6"/>
-      <c r="K36" s="6"/>
+      <c r="B36" s="10"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="10"/>
+      <c r="I36" s="10"/>
+      <c r="J36" s="10"/>
+      <c r="K36" s="10"/>
       <c r="L36" s="16"/>
     </row>
-    <row r="37" spans="1:12" ht="19.95" customHeight="1">
+    <row r="37" spans="1:12">
       <c r="A37" s="15"/>
-      <c r="B37" s="6"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6"/>
-      <c r="J37" s="6"/>
-      <c r="K37" s="6"/>
+      <c r="B37" s="10"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="10"/>
+      <c r="I37" s="10"/>
+      <c r="J37" s="10"/>
+      <c r="K37" s="10"/>
       <c r="L37" s="16"/>
     </row>
-    <row r="38" spans="1:12" ht="19.95" customHeight="1">
+    <row r="38" spans="1:12">
       <c r="A38" s="15"/>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="6"/>
-      <c r="K38" s="6"/>
+      <c r="B38" s="10"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="10"/>
+      <c r="G38" s="10"/>
+      <c r="H38" s="10"/>
+      <c r="I38" s="10"/>
+      <c r="J38" s="10"/>
+      <c r="K38" s="10"/>
       <c r="L38" s="16"/>
     </row>
-    <row r="39" spans="1:12" ht="19.95" customHeight="1">
+    <row r="39" spans="1:12">
       <c r="A39" s="15"/>
-      <c r="B39" s="6"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="6"/>
-      <c r="K39" s="6"/>
+      <c r="B39" s="10"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="10"/>
+      <c r="F39" s="10"/>
+      <c r="G39" s="10"/>
+      <c r="H39" s="10"/>
+      <c r="I39" s="10"/>
+      <c r="J39" s="10"/>
+      <c r="K39" s="10"/>
       <c r="L39" s="16"/>
     </row>
-    <row r="40" spans="1:12" ht="19.95" customHeight="1">
+    <row r="40" spans="1:12">
       <c r="A40" s="17"/>
       <c r="B40" s="18"/>
       <c r="C40" s="18"/>
@@ -3771,314 +3754,309 @@
       <c r="K40" s="18"/>
       <c r="L40" s="19"/>
     </row>
-    <row r="41" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="42" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="43" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="44" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="45" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="46" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="47" spans="1:12" ht="24" customHeight="1">
-      <c r="A47" s="22" t="s">
-        <v>93</v>
-      </c>
-      <c r="B47" s="10"/>
-      <c r="C47" s="10"/>
-      <c r="D47" s="10"/>
-      <c r="E47" s="10"/>
-      <c r="F47" s="10"/>
-      <c r="G47" s="10"/>
-      <c r="H47" s="10"/>
-      <c r="I47" s="10"/>
-      <c r="J47" s="10"/>
-      <c r="K47" s="10"/>
-      <c r="L47" s="8"/>
-    </row>
-    <row r="48" spans="1:12" ht="19.95" customHeight="1">
+    <row r="47" spans="1:12">
+      <c r="A47" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="8"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="8"/>
+      <c r="I47" s="8"/>
+      <c r="J47" s="8"/>
+      <c r="K47" s="8"/>
+      <c r="L47" s="6"/>
+    </row>
+    <row r="48" spans="1:12" ht="16.2">
       <c r="A48" s="4" t="s">
         <v>48</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="F48" s="24"/>
-      <c r="G48" s="10"/>
-      <c r="H48" s="10"/>
-      <c r="I48" s="10"/>
-      <c r="J48" s="10"/>
-      <c r="K48" s="10"/>
-      <c r="L48" s="8"/>
-    </row>
-    <row r="49" spans="1:12" ht="19.95" customHeight="1">
+        <v>98</v>
+      </c>
+      <c r="F48" s="22"/>
+      <c r="G48" s="8"/>
+      <c r="H48" s="8"/>
+      <c r="I48" s="8"/>
+      <c r="J48" s="8"/>
+      <c r="K48" s="8"/>
+      <c r="L48" s="6"/>
+    </row>
+    <row r="49" spans="1:12" ht="16.2">
       <c r="A49" s="1">
         <v>1</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F49" s="12"/>
-      <c r="G49" s="10"/>
-      <c r="H49" s="10"/>
-      <c r="I49" s="10"/>
-      <c r="J49" s="10"/>
-      <c r="K49" s="10"/>
-      <c r="L49" s="8"/>
-    </row>
-    <row r="50" spans="1:12" ht="31.95" customHeight="1">
+      <c r="G49" s="8"/>
+      <c r="H49" s="8"/>
+      <c r="I49" s="8"/>
+      <c r="J49" s="8"/>
+      <c r="K49" s="8"/>
+      <c r="L49" s="6"/>
+    </row>
+    <row r="50" spans="1:12" ht="16.2">
       <c r="A50" s="1">
         <v>2</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F50" s="12"/>
-      <c r="G50" s="10"/>
-      <c r="H50" s="10"/>
-      <c r="I50" s="10"/>
-      <c r="J50" s="10"/>
-      <c r="K50" s="10"/>
-      <c r="L50" s="8"/>
-    </row>
-    <row r="51" spans="1:12" ht="19.95" customHeight="1">
+      <c r="G50" s="8"/>
+      <c r="H50" s="8"/>
+      <c r="I50" s="8"/>
+      <c r="J50" s="8"/>
+      <c r="K50" s="8"/>
+      <c r="L50" s="6"/>
+    </row>
+    <row r="51" spans="1:12" ht="16.2">
       <c r="A51" s="1">
         <v>3</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F51" s="12"/>
-      <c r="G51" s="10"/>
-      <c r="H51" s="10"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="10"/>
-      <c r="K51" s="10"/>
-      <c r="L51" s="8"/>
-    </row>
-    <row r="52" spans="1:12" ht="19.95" customHeight="1">
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="6"/>
+    </row>
+    <row r="52" spans="1:12" ht="16.2">
       <c r="A52" s="1">
         <v>4</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F52" s="12"/>
-      <c r="G52" s="10"/>
-      <c r="H52" s="10"/>
-      <c r="I52" s="10"/>
-      <c r="J52" s="10"/>
-      <c r="K52" s="10"/>
-      <c r="L52" s="8"/>
-    </row>
-    <row r="53" spans="1:12" ht="19.95" customHeight="1">
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="8"/>
+      <c r="J52" s="8"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="6"/>
+    </row>
+    <row r="53" spans="1:12" ht="16.2">
       <c r="A53" s="1">
         <v>5</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="F53" s="12"/>
-      <c r="G53" s="10"/>
-      <c r="H53" s="10"/>
-      <c r="I53" s="10"/>
-      <c r="J53" s="10"/>
-      <c r="K53" s="10"/>
-      <c r="L53" s="8"/>
-    </row>
-    <row r="54" spans="1:12" ht="19.95" customHeight="1">
+      <c r="G53" s="8"/>
+      <c r="H53" s="8"/>
+      <c r="I53" s="8"/>
+      <c r="J53" s="8"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="6"/>
+    </row>
+    <row r="54" spans="1:12" ht="16.2">
       <c r="A54" s="1">
         <v>6</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F54" s="12"/>
-      <c r="G54" s="10"/>
-      <c r="H54" s="10"/>
-      <c r="I54" s="10"/>
-      <c r="J54" s="10"/>
-      <c r="K54" s="10"/>
-      <c r="L54" s="8"/>
-    </row>
-    <row r="55" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="56" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="57" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="58" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="59" spans="1:12" ht="24" customHeight="1">
-      <c r="A59" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="B59" s="10"/>
-      <c r="C59" s="10"/>
-      <c r="D59" s="10"/>
-      <c r="E59" s="10"/>
-      <c r="F59" s="10"/>
-      <c r="G59" s="10"/>
-      <c r="H59" s="10"/>
-      <c r="I59" s="10"/>
-      <c r="J59" s="10"/>
-      <c r="K59" s="10"/>
-      <c r="L59" s="8"/>
-    </row>
-    <row r="60" spans="1:12" ht="19.95" customHeight="1">
+      <c r="G54" s="8"/>
+      <c r="H54" s="8"/>
+      <c r="I54" s="8"/>
+      <c r="J54" s="8"/>
+      <c r="K54" s="8"/>
+      <c r="L54" s="6"/>
+    </row>
+    <row r="59" spans="1:12">
+      <c r="A59" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="B59" s="8"/>
+      <c r="C59" s="8"/>
+      <c r="D59" s="8"/>
+      <c r="E59" s="8"/>
+      <c r="F59" s="8"/>
+      <c r="G59" s="8"/>
+      <c r="H59" s="8"/>
+      <c r="I59" s="8"/>
+      <c r="J59" s="8"/>
+      <c r="K59" s="8"/>
+      <c r="L59" s="6"/>
+    </row>
+    <row r="60" spans="1:12" ht="16.2">
       <c r="A60" s="4" t="s">
         <v>48</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E60" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F60" s="24"/>
-      <c r="G60" s="10"/>
-      <c r="H60" s="10"/>
-      <c r="I60" s="10"/>
-      <c r="J60" s="10"/>
-      <c r="K60" s="10"/>
-      <c r="L60" s="8"/>
-    </row>
-    <row r="61" spans="1:12" ht="19.95" customHeight="1">
+      <c r="F60" s="22"/>
+      <c r="G60" s="8"/>
+      <c r="H60" s="8"/>
+      <c r="I60" s="8"/>
+      <c r="J60" s="8"/>
+      <c r="K60" s="8"/>
+      <c r="L60" s="6"/>
+    </row>
+    <row r="61" spans="1:12" ht="16.2">
       <c r="A61" s="1">
         <v>1</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F61" s="12"/>
-      <c r="G61" s="10"/>
-      <c r="H61" s="10"/>
-      <c r="I61" s="10"/>
-      <c r="J61" s="10"/>
-      <c r="K61" s="10"/>
-      <c r="L61" s="8"/>
-    </row>
-    <row r="62" spans="1:12" ht="19.95" customHeight="1">
+      <c r="G61" s="8"/>
+      <c r="H61" s="8"/>
+      <c r="I61" s="8"/>
+      <c r="J61" s="8"/>
+      <c r="K61" s="8"/>
+      <c r="L61" s="6"/>
+    </row>
+    <row r="62" spans="1:12" ht="16.2">
       <c r="A62" s="1">
         <v>2</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F62" s="12"/>
-      <c r="G62" s="10"/>
-      <c r="H62" s="10"/>
-      <c r="I62" s="10"/>
-      <c r="J62" s="10"/>
-      <c r="K62" s="10"/>
-      <c r="L62" s="8"/>
-    </row>
-    <row r="63" spans="1:12" ht="19.95" customHeight="1">
+      <c r="G62" s="8"/>
+      <c r="H62" s="8"/>
+      <c r="I62" s="8"/>
+      <c r="J62" s="8"/>
+      <c r="K62" s="8"/>
+      <c r="L62" s="6"/>
+    </row>
+    <row r="63" spans="1:12" ht="16.2">
       <c r="A63" s="1">
         <v>3</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F63" s="12"/>
-      <c r="G63" s="10"/>
-      <c r="H63" s="10"/>
-      <c r="I63" s="10"/>
-      <c r="J63" s="10"/>
-      <c r="K63" s="10"/>
-      <c r="L63" s="8"/>
+      <c r="G63" s="8"/>
+      <c r="H63" s="8"/>
+      <c r="I63" s="8"/>
+      <c r="J63" s="8"/>
+      <c r="K63" s="8"/>
+      <c r="L63" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="G8:L8"/>
+    <mergeCell ref="F62:L62"/>
+    <mergeCell ref="F12:L20"/>
+    <mergeCell ref="G7:L7"/>
     <mergeCell ref="F63:L63"/>
     <mergeCell ref="A4:L4"/>
     <mergeCell ref="A34:L34"/>
@@ -4088,6 +4066,7 @@
     <mergeCell ref="F50:L50"/>
     <mergeCell ref="A11:L11"/>
     <mergeCell ref="A12:E20"/>
+    <mergeCell ref="A2:L2"/>
     <mergeCell ref="G5:L5"/>
     <mergeCell ref="A47:L47"/>
     <mergeCell ref="F53:L53"/>
@@ -4095,12 +4074,6 @@
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="A21:L21"/>
     <mergeCell ref="A35:L40"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="G8:L8"/>
-    <mergeCell ref="F62:L62"/>
-    <mergeCell ref="F12:L20"/>
-    <mergeCell ref="G7:L7"/>
-    <mergeCell ref="A2:L2"/>
     <mergeCell ref="F60:L60"/>
     <mergeCell ref="F49:L49"/>
     <mergeCell ref="F54:L54"/>
@@ -4112,7 +4085,7 @@
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" scale="43" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="24" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4121,176 +4094,174 @@
   <dimension ref="A1:L63"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
-    <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="23" customWidth="1"/>
-    <col min="11" max="11" width="28" customWidth="1"/>
-    <col min="12" max="12" width="26" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="61.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="36" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="47.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="30" customHeight="1">
+    <row r="1" spans="1:12">
       <c r="A1" s="11" t="s">
-        <v>195</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-    </row>
-    <row r="2" spans="1:12" ht="19.95" customHeight="1">
+        <v>198</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-    </row>
-    <row r="3" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="4" spans="1:12" ht="24" customHeight="1">
-      <c r="A4" s="22" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="8"/>
-    </row>
-    <row r="5" spans="1:12" ht="19.95" customHeight="1">
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="6"/>
+    </row>
+    <row r="5" spans="1:12" ht="16.2">
       <c r="A5" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>201</v>
-      </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="8"/>
+        <v>204</v>
+      </c>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="6"/>
       <c r="F5" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="8"/>
-    </row>
-    <row r="6" spans="1:12" ht="19.95" customHeight="1">
+        <v>205</v>
+      </c>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="6"/>
+    </row>
+    <row r="6" spans="1:12" ht="16.2">
       <c r="A6" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="8"/>
+        <v>206</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="6"/>
       <c r="F6" s="3" t="s">
         <v>35</v>
       </c>
       <c r="G6" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="8"/>
-    </row>
-    <row r="7" spans="1:12" ht="19.95" customHeight="1">
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="6"/>
+    </row>
+    <row r="7" spans="1:12" ht="16.2">
       <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="8"/>
+        <v>207</v>
+      </c>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="6"/>
       <c r="F7" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>205</v>
-      </c>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="8"/>
-    </row>
-    <row r="8" spans="1:12" ht="19.95" customHeight="1">
+        <v>208</v>
+      </c>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="6"/>
+    </row>
+    <row r="8" spans="1:12" ht="16.2">
       <c r="A8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>206</v>
-      </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="8"/>
+        <v>209</v>
+      </c>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="6"/>
       <c r="F8" s="3" t="s">
         <v>42</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="8"/>
-    </row>
-    <row r="9" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="10" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="11" spans="1:12" ht="24" customHeight="1">
-      <c r="A11" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="6"/>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="8"/>
-    </row>
-    <row r="12" spans="1:12" ht="64.05" customHeight="1">
-      <c r="A12" s="23" t="s">
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="6"/>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="25" t="s">
         <v>45</v>
       </c>
       <c r="B12" s="13"/>
@@ -4298,7 +4269,7 @@
       <c r="D12" s="13"/>
       <c r="E12" s="14"/>
       <c r="F12" s="12" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13"/>
@@ -4307,105 +4278,105 @@
       <c r="K12" s="13"/>
       <c r="L12" s="14"/>
     </row>
-    <row r="13" spans="1:12" ht="19.95" customHeight="1">
+    <row r="13" spans="1:12">
       <c r="A13" s="15"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
       <c r="E13" s="16"/>
       <c r="F13" s="15"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
       <c r="L13" s="16"/>
     </row>
-    <row r="14" spans="1:12" ht="19.95" customHeight="1">
+    <row r="14" spans="1:12">
       <c r="A14" s="15"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
       <c r="E14" s="16"/>
       <c r="F14" s="15"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
       <c r="L14" s="16"/>
     </row>
-    <row r="15" spans="1:12" ht="19.95" customHeight="1">
+    <row r="15" spans="1:12">
       <c r="A15" s="15"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
       <c r="E15" s="16"/>
       <c r="F15" s="15"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
       <c r="L15" s="16"/>
     </row>
-    <row r="16" spans="1:12" ht="19.95" customHeight="1">
+    <row r="16" spans="1:12">
       <c r="A16" s="15"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
       <c r="E16" s="16"/>
       <c r="F16" s="15"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10"/>
       <c r="L16" s="16"/>
     </row>
-    <row r="17" spans="1:12" ht="19.95" customHeight="1">
+    <row r="17" spans="1:12">
       <c r="A17" s="15"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
       <c r="E17" s="16"/>
       <c r="F17" s="15"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
       <c r="L17" s="16"/>
     </row>
-    <row r="18" spans="1:12" ht="19.95" customHeight="1">
+    <row r="18" spans="1:12">
       <c r="A18" s="15"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
       <c r="E18" s="16"/>
       <c r="F18" s="15"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10"/>
       <c r="L18" s="16"/>
     </row>
-    <row r="19" spans="1:12" ht="19.95" customHeight="1">
+    <row r="19" spans="1:12">
       <c r="A19" s="15"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
       <c r="E19" s="16"/>
       <c r="F19" s="15"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10"/>
       <c r="L19" s="16"/>
     </row>
-    <row r="20" spans="1:12" ht="19.95" customHeight="1">
+    <row r="20" spans="1:12">
       <c r="A20" s="17"/>
       <c r="B20" s="18"/>
       <c r="C20" s="18"/>
@@ -4419,23 +4390,23 @@
       <c r="K20" s="18"/>
       <c r="L20" s="19"/>
     </row>
-    <row r="21" spans="1:12" ht="24" customHeight="1">
-      <c r="A21" s="22" t="s">
+    <row r="21" spans="1:12">
+      <c r="A21" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="8"/>
-    </row>
-    <row r="22" spans="1:12" ht="19.95" customHeight="1">
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="6"/>
+    </row>
+    <row r="22" spans="1:12" ht="16.2">
       <c r="A22" s="4" t="s">
         <v>48</v>
       </c>
@@ -4473,53 +4444,53 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="19.95" customHeight="1">
+    <row r="23" spans="1:12" ht="16.2">
       <c r="A23" s="1">
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>79</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>65</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>79</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="19.95" customHeight="1">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="16.2">
       <c r="A24" s="1">
         <v>2</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>78</v>
@@ -4537,7 +4508,7 @@
         <v>65</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>79</v>
@@ -4546,18 +4517,18 @@
         <v>79</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="19.95" customHeight="1">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="16.2">
       <c r="A25" s="1">
         <v>3</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>78</v>
@@ -4575,7 +4546,7 @@
         <v>65</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>79</v>
@@ -4584,21 +4555,21 @@
         <v>79</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="19.95" customHeight="1">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="16.2">
       <c r="A26" s="1">
         <v>4</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>79</v>
@@ -4613,33 +4584,33 @@
         <v>65</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>79</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="19.95" customHeight="1">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="16.2">
       <c r="A27" s="1">
         <v>5</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>79</v>
@@ -4648,112 +4619,112 @@
         <v>79</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="19.95" customHeight="1">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="16.2">
       <c r="A28" s="1">
         <v>6</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H28" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="D28" s="2" t="s">
+      <c r="I28" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="L28" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="19.95" customHeight="1">
+    </row>
+    <row r="29" spans="1:12" ht="16.2">
       <c r="A29" s="1">
         <v>7</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="E29" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="F29" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="L29" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="L29" s="2" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="19.95" customHeight="1">
+    </row>
+    <row r="30" spans="1:12" ht="16.2">
       <c r="A30" s="1">
         <v>8</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>79</v>
@@ -4762,36 +4733,36 @@
         <v>79</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="31.95" customHeight="1">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="16.2">
       <c r="A31" s="1">
         <v>9</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>79</v>
@@ -4800,71 +4771,71 @@
         <v>79</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" ht="19.95" customHeight="1">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="16.2">
       <c r="A32" s="1">
         <v>10</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>79</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H32" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="L32" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="I32" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="L32" s="2" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" ht="19.95" customHeight="1">
+    </row>
+    <row r="33" spans="1:12" ht="16.2">
       <c r="A33" s="1">
         <v>11</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>79</v>
@@ -4879,7 +4850,7 @@
         <v>65</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>79</v>
@@ -4888,28 +4859,28 @@
         <v>79</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" ht="24" customHeight="1">
-      <c r="A34" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="10"/>
-      <c r="J34" s="10"/>
-      <c r="K34" s="10"/>
-      <c r="L34" s="8"/>
-    </row>
-    <row r="35" spans="1:12" ht="48" customHeight="1">
-      <c r="A35" s="25" t="s">
-        <v>259</v>
+        <v>260</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="6"/>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35" s="24" t="s">
+        <v>261</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -4923,63 +4894,63 @@
       <c r="K35" s="13"/>
       <c r="L35" s="14"/>
     </row>
-    <row r="36" spans="1:12" ht="19.95" customHeight="1">
+    <row r="36" spans="1:12">
       <c r="A36" s="15"/>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="6"/>
-      <c r="J36" s="6"/>
-      <c r="K36" s="6"/>
+      <c r="B36" s="10"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="10"/>
+      <c r="I36" s="10"/>
+      <c r="J36" s="10"/>
+      <c r="K36" s="10"/>
       <c r="L36" s="16"/>
     </row>
-    <row r="37" spans="1:12" ht="19.95" customHeight="1">
+    <row r="37" spans="1:12">
       <c r="A37" s="15"/>
-      <c r="B37" s="6"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6"/>
-      <c r="J37" s="6"/>
-      <c r="K37" s="6"/>
+      <c r="B37" s="10"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="10"/>
+      <c r="I37" s="10"/>
+      <c r="J37" s="10"/>
+      <c r="K37" s="10"/>
       <c r="L37" s="16"/>
     </row>
-    <row r="38" spans="1:12" ht="19.95" customHeight="1">
+    <row r="38" spans="1:12">
       <c r="A38" s="15"/>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="6"/>
-      <c r="K38" s="6"/>
+      <c r="B38" s="10"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="10"/>
+      <c r="G38" s="10"/>
+      <c r="H38" s="10"/>
+      <c r="I38" s="10"/>
+      <c r="J38" s="10"/>
+      <c r="K38" s="10"/>
       <c r="L38" s="16"/>
     </row>
-    <row r="39" spans="1:12" ht="19.95" customHeight="1">
+    <row r="39" spans="1:12">
       <c r="A39" s="15"/>
-      <c r="B39" s="6"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="6"/>
-      <c r="K39" s="6"/>
+      <c r="B39" s="10"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="10"/>
+      <c r="F39" s="10"/>
+      <c r="G39" s="10"/>
+      <c r="H39" s="10"/>
+      <c r="I39" s="10"/>
+      <c r="J39" s="10"/>
+      <c r="K39" s="10"/>
       <c r="L39" s="16"/>
     </row>
-    <row r="40" spans="1:12" ht="19.95" customHeight="1">
+    <row r="40" spans="1:12">
       <c r="A40" s="17"/>
       <c r="B40" s="18"/>
       <c r="C40" s="18"/>
@@ -4993,291 +4964,285 @@
       <c r="K40" s="18"/>
       <c r="L40" s="19"/>
     </row>
-    <row r="41" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="42" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="43" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="44" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="45" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="46" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="47" spans="1:12" ht="24" customHeight="1">
-      <c r="A47" s="22" t="s">
-        <v>93</v>
-      </c>
-      <c r="B47" s="10"/>
-      <c r="C47" s="10"/>
-      <c r="D47" s="10"/>
-      <c r="E47" s="10"/>
-      <c r="F47" s="10"/>
-      <c r="G47" s="10"/>
-      <c r="H47" s="10"/>
-      <c r="I47" s="10"/>
-      <c r="J47" s="10"/>
-      <c r="K47" s="10"/>
-      <c r="L47" s="8"/>
-    </row>
-    <row r="48" spans="1:12" ht="19.95" customHeight="1">
+    <row r="47" spans="1:12">
+      <c r="A47" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="8"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="8"/>
+      <c r="I47" s="8"/>
+      <c r="J47" s="8"/>
+      <c r="K47" s="8"/>
+      <c r="L47" s="6"/>
+    </row>
+    <row r="48" spans="1:12" ht="16.2">
       <c r="A48" s="4" t="s">
         <v>48</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="F48" s="24"/>
-      <c r="G48" s="10"/>
-      <c r="H48" s="10"/>
-      <c r="I48" s="10"/>
-      <c r="J48" s="10"/>
-      <c r="K48" s="10"/>
-      <c r="L48" s="8"/>
-    </row>
-    <row r="49" spans="1:12" ht="19.95" customHeight="1">
+        <v>98</v>
+      </c>
+      <c r="F48" s="22"/>
+      <c r="G48" s="8"/>
+      <c r="H48" s="8"/>
+      <c r="I48" s="8"/>
+      <c r="J48" s="8"/>
+      <c r="K48" s="8"/>
+      <c r="L48" s="6"/>
+    </row>
+    <row r="49" spans="1:12" ht="16.2">
       <c r="A49" s="1">
         <v>1</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F49" s="12"/>
-      <c r="G49" s="10"/>
-      <c r="H49" s="10"/>
-      <c r="I49" s="10"/>
-      <c r="J49" s="10"/>
-      <c r="K49" s="10"/>
-      <c r="L49" s="8"/>
-    </row>
-    <row r="50" spans="1:12" ht="19.95" customHeight="1">
+      <c r="G49" s="8"/>
+      <c r="H49" s="8"/>
+      <c r="I49" s="8"/>
+      <c r="J49" s="8"/>
+      <c r="K49" s="8"/>
+      <c r="L49" s="6"/>
+    </row>
+    <row r="50" spans="1:12" ht="16.2">
       <c r="A50" s="1">
         <v>2</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F50" s="12"/>
-      <c r="G50" s="10"/>
-      <c r="H50" s="10"/>
-      <c r="I50" s="10"/>
-      <c r="J50" s="10"/>
-      <c r="K50" s="10"/>
-      <c r="L50" s="8"/>
-    </row>
-    <row r="51" spans="1:12" ht="19.95" customHeight="1">
+      <c r="G50" s="8"/>
+      <c r="H50" s="8"/>
+      <c r="I50" s="8"/>
+      <c r="J50" s="8"/>
+      <c r="K50" s="8"/>
+      <c r="L50" s="6"/>
+    </row>
+    <row r="51" spans="1:12" ht="16.2">
       <c r="A51" s="1">
         <v>3</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F51" s="12"/>
-      <c r="G51" s="10"/>
-      <c r="H51" s="10"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="10"/>
-      <c r="K51" s="10"/>
-      <c r="L51" s="8"/>
-    </row>
-    <row r="52" spans="1:12" ht="31.95" customHeight="1">
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="6"/>
+    </row>
+    <row r="52" spans="1:12" ht="16.2">
       <c r="A52" s="1">
         <v>4</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F52" s="12"/>
-      <c r="G52" s="10"/>
-      <c r="H52" s="10"/>
-      <c r="I52" s="10"/>
-      <c r="J52" s="10"/>
-      <c r="K52" s="10"/>
-      <c r="L52" s="8"/>
-    </row>
-    <row r="53" spans="1:12" ht="31.95" customHeight="1">
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="8"/>
+      <c r="J52" s="8"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="6"/>
+    </row>
+    <row r="53" spans="1:12" ht="16.2">
       <c r="A53" s="1">
         <v>5</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F53" s="12"/>
-      <c r="G53" s="10"/>
-      <c r="H53" s="10"/>
-      <c r="I53" s="10"/>
-      <c r="J53" s="10"/>
-      <c r="K53" s="10"/>
-      <c r="L53" s="8"/>
-    </row>
-    <row r="54" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="55" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="56" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="57" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="58" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="59" spans="1:12" ht="24" customHeight="1">
-      <c r="A59" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="B59" s="10"/>
-      <c r="C59" s="10"/>
-      <c r="D59" s="10"/>
-      <c r="E59" s="10"/>
-      <c r="F59" s="10"/>
-      <c r="G59" s="10"/>
-      <c r="H59" s="10"/>
-      <c r="I59" s="10"/>
-      <c r="J59" s="10"/>
-      <c r="K59" s="10"/>
-      <c r="L59" s="8"/>
-    </row>
-    <row r="60" spans="1:12" ht="19.95" customHeight="1">
+      <c r="G53" s="8"/>
+      <c r="H53" s="8"/>
+      <c r="I53" s="8"/>
+      <c r="J53" s="8"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="6"/>
+    </row>
+    <row r="59" spans="1:12">
+      <c r="A59" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="B59" s="8"/>
+      <c r="C59" s="8"/>
+      <c r="D59" s="8"/>
+      <c r="E59" s="8"/>
+      <c r="F59" s="8"/>
+      <c r="G59" s="8"/>
+      <c r="H59" s="8"/>
+      <c r="I59" s="8"/>
+      <c r="J59" s="8"/>
+      <c r="K59" s="8"/>
+      <c r="L59" s="6"/>
+    </row>
+    <row r="60" spans="1:12" ht="16.2">
       <c r="A60" s="4" t="s">
         <v>48</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E60" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F60" s="24"/>
-      <c r="G60" s="10"/>
-      <c r="H60" s="10"/>
-      <c r="I60" s="10"/>
-      <c r="J60" s="10"/>
-      <c r="K60" s="10"/>
-      <c r="L60" s="8"/>
-    </row>
-    <row r="61" spans="1:12" ht="19.95" customHeight="1">
+      <c r="F60" s="22"/>
+      <c r="G60" s="8"/>
+      <c r="H60" s="8"/>
+      <c r="I60" s="8"/>
+      <c r="J60" s="8"/>
+      <c r="K60" s="8"/>
+      <c r="L60" s="6"/>
+    </row>
+    <row r="61" spans="1:12" ht="16.2">
       <c r="A61" s="1">
         <v>1</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F61" s="12"/>
-      <c r="G61" s="10"/>
-      <c r="H61" s="10"/>
-      <c r="I61" s="10"/>
-      <c r="J61" s="10"/>
-      <c r="K61" s="10"/>
-      <c r="L61" s="8"/>
-    </row>
-    <row r="62" spans="1:12" ht="19.95" customHeight="1">
+      <c r="G61" s="8"/>
+      <c r="H61" s="8"/>
+      <c r="I61" s="8"/>
+      <c r="J61" s="8"/>
+      <c r="K61" s="8"/>
+      <c r="L61" s="6"/>
+    </row>
+    <row r="62" spans="1:12" ht="16.2">
       <c r="A62" s="1">
         <v>2</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D62" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="E62" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="E62" s="2" t="s">
-        <v>270</v>
-      </c>
       <c r="F62" s="12"/>
-      <c r="G62" s="10"/>
-      <c r="H62" s="10"/>
-      <c r="I62" s="10"/>
-      <c r="J62" s="10"/>
-      <c r="K62" s="10"/>
-      <c r="L62" s="8"/>
-    </row>
-    <row r="63" spans="1:12" ht="19.95" customHeight="1">
+      <c r="G62" s="8"/>
+      <c r="H62" s="8"/>
+      <c r="I62" s="8"/>
+      <c r="J62" s="8"/>
+      <c r="K62" s="8"/>
+      <c r="L62" s="6"/>
+    </row>
+    <row r="63" spans="1:12" ht="16.2">
       <c r="A63" s="1">
         <v>3</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>79</v>
       </c>
       <c r="F63" s="12"/>
-      <c r="G63" s="10"/>
-      <c r="H63" s="10"/>
-      <c r="I63" s="10"/>
-      <c r="J63" s="10"/>
-      <c r="K63" s="10"/>
-      <c r="L63" s="8"/>
+      <c r="G63" s="8"/>
+      <c r="H63" s="8"/>
+      <c r="I63" s="8"/>
+      <c r="J63" s="8"/>
+      <c r="K63" s="8"/>
+      <c r="L63" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="G8:L8"/>
+    <mergeCell ref="F62:L62"/>
+    <mergeCell ref="F12:L20"/>
+    <mergeCell ref="G7:L7"/>
     <mergeCell ref="F63:L63"/>
     <mergeCell ref="A4:L4"/>
     <mergeCell ref="A34:L34"/>
@@ -5287,6 +5252,7 @@
     <mergeCell ref="F50:L50"/>
     <mergeCell ref="A11:L11"/>
     <mergeCell ref="A12:E20"/>
+    <mergeCell ref="A2:L2"/>
     <mergeCell ref="G5:L5"/>
     <mergeCell ref="A47:L47"/>
     <mergeCell ref="F53:L53"/>
@@ -5294,12 +5260,6 @@
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="A21:L21"/>
     <mergeCell ref="A35:L40"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="G8:L8"/>
-    <mergeCell ref="F62:L62"/>
-    <mergeCell ref="F12:L20"/>
-    <mergeCell ref="G7:L7"/>
-    <mergeCell ref="A2:L2"/>
     <mergeCell ref="F60:L60"/>
     <mergeCell ref="F49:L49"/>
     <mergeCell ref="F52:L52"/>
@@ -5310,7 +5270,7 @@
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" scale="43" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="26" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5319,176 +5279,173 @@
   <dimension ref="A1:L62"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
-    <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="23" customWidth="1"/>
-    <col min="11" max="11" width="28" customWidth="1"/>
-    <col min="12" max="12" width="26" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="29.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="53.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="33.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="30" customHeight="1">
+    <row r="1" spans="1:12">
       <c r="A1" s="11" t="s">
-        <v>274</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-    </row>
-    <row r="2" spans="1:12" ht="19.95" customHeight="1">
+        <v>276</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-    </row>
-    <row r="3" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="4" spans="1:12" ht="24" customHeight="1">
-      <c r="A4" s="22" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="8"/>
-    </row>
-    <row r="5" spans="1:12" ht="19.95" customHeight="1">
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="6"/>
+    </row>
+    <row r="5" spans="1:12" ht="16.2">
       <c r="A5" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>275</v>
-      </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="8"/>
+        <v>277</v>
+      </c>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="6"/>
       <c r="F5" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>276</v>
-      </c>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="8"/>
-    </row>
-    <row r="6" spans="1:12" ht="19.95" customHeight="1">
+        <v>278</v>
+      </c>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="6"/>
+    </row>
+    <row r="6" spans="1:12" ht="16.2">
       <c r="A6" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>277</v>
-      </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="8"/>
+        <v>279</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="6"/>
       <c r="F6" s="3" t="s">
         <v>35</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>278</v>
-      </c>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="8"/>
-    </row>
-    <row r="7" spans="1:12" ht="19.95" customHeight="1">
+        <v>280</v>
+      </c>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="6"/>
+    </row>
+    <row r="7" spans="1:12" ht="16.2">
       <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>279</v>
-      </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="8"/>
+        <v>281</v>
+      </c>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="6"/>
       <c r="F7" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="8"/>
-    </row>
-    <row r="8" spans="1:12" ht="19.95" customHeight="1">
+        <v>282</v>
+      </c>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="6"/>
+    </row>
+    <row r="8" spans="1:12" ht="16.2">
       <c r="A8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>281</v>
-      </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="8"/>
+        <v>283</v>
+      </c>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="6"/>
       <c r="F8" s="3" t="s">
         <v>42</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>282</v>
-      </c>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="8"/>
-    </row>
-    <row r="9" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="10" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="11" spans="1:12" ht="24" customHeight="1">
-      <c r="A11" s="22" t="s">
+        <v>284</v>
+      </c>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="6"/>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="8"/>
-    </row>
-    <row r="12" spans="1:12" ht="90" customHeight="1">
-      <c r="A12" s="23" t="s">
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="6"/>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="25" t="s">
         <v>45</v>
       </c>
       <c r="B12" s="13"/>
@@ -5496,7 +5453,7 @@
       <c r="D12" s="13"/>
       <c r="E12" s="14"/>
       <c r="F12" s="12" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13"/>
@@ -5505,105 +5462,105 @@
       <c r="K12" s="13"/>
       <c r="L12" s="14"/>
     </row>
-    <row r="13" spans="1:12" ht="19.95" customHeight="1">
+    <row r="13" spans="1:12">
       <c r="A13" s="15"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
       <c r="E13" s="16"/>
       <c r="F13" s="15"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
       <c r="L13" s="16"/>
     </row>
-    <row r="14" spans="1:12" ht="19.95" customHeight="1">
+    <row r="14" spans="1:12">
       <c r="A14" s="15"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
       <c r="E14" s="16"/>
       <c r="F14" s="15"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
       <c r="L14" s="16"/>
     </row>
-    <row r="15" spans="1:12" ht="19.95" customHeight="1">
+    <row r="15" spans="1:12">
       <c r="A15" s="15"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
       <c r="E15" s="16"/>
       <c r="F15" s="15"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
       <c r="L15" s="16"/>
     </row>
-    <row r="16" spans="1:12" ht="19.95" customHeight="1">
+    <row r="16" spans="1:12">
       <c r="A16" s="15"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
       <c r="E16" s="16"/>
       <c r="F16" s="15"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10"/>
       <c r="L16" s="16"/>
     </row>
-    <row r="17" spans="1:12" ht="19.95" customHeight="1">
+    <row r="17" spans="1:12">
       <c r="A17" s="15"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
       <c r="E17" s="16"/>
       <c r="F17" s="15"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
       <c r="L17" s="16"/>
     </row>
-    <row r="18" spans="1:12" ht="19.95" customHeight="1">
+    <row r="18" spans="1:12">
       <c r="A18" s="15"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
       <c r="E18" s="16"/>
       <c r="F18" s="15"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10"/>
       <c r="L18" s="16"/>
     </row>
-    <row r="19" spans="1:12" ht="19.95" customHeight="1">
+    <row r="19" spans="1:12">
       <c r="A19" s="15"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
       <c r="E19" s="16"/>
       <c r="F19" s="15"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10"/>
       <c r="L19" s="16"/>
     </row>
-    <row r="20" spans="1:12" ht="19.95" customHeight="1">
+    <row r="20" spans="1:12">
       <c r="A20" s="17"/>
       <c r="B20" s="18"/>
       <c r="C20" s="18"/>
@@ -5617,23 +5574,23 @@
       <c r="K20" s="18"/>
       <c r="L20" s="19"/>
     </row>
-    <row r="21" spans="1:12" ht="24" customHeight="1">
-      <c r="A21" s="22" t="s">
+    <row r="21" spans="1:12">
+      <c r="A21" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="8"/>
-    </row>
-    <row r="22" spans="1:12" ht="19.95" customHeight="1">
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="6"/>
+    </row>
+    <row r="22" spans="1:12" ht="16.2">
       <c r="A22" s="4" t="s">
         <v>48</v>
       </c>
@@ -5671,18 +5628,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="19.95" customHeight="1">
+    <row r="23" spans="1:12" ht="16.2">
       <c r="A23" s="1">
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>79</v>
@@ -5694,10 +5651,10 @@
         <v>79</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>79</v>
@@ -5706,59 +5663,59 @@
         <v>79</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="19.95" customHeight="1">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="16.2">
       <c r="A24" s="1">
         <v>2</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="J24" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="L24" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="19.95" customHeight="1">
+    </row>
+    <row r="25" spans="1:12" ht="16.2">
       <c r="A25" s="1">
         <v>3</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>79</v>
@@ -5770,10 +5727,10 @@
         <v>79</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>79</v>
@@ -5782,21 +5739,21 @@
         <v>79</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="19.95" customHeight="1">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="16.2">
       <c r="A26" s="1">
         <v>4</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>79</v>
@@ -5805,51 +5762,51 @@
         <v>79</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>79</v>
+        <v>296</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>79</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="19.95" customHeight="1">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="16.2">
       <c r="A27" s="1">
         <v>5</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>79</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>65</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>79</v>
@@ -5858,34 +5815,28 @@
         <v>79</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="29" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="30" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="31" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="32" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="33" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="34" spans="1:12" ht="24" customHeight="1">
-      <c r="A34" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="10"/>
-      <c r="J34" s="10"/>
-      <c r="K34" s="10"/>
-      <c r="L34" s="8"/>
-    </row>
-    <row r="35" spans="1:12" ht="48" customHeight="1">
-      <c r="A35" s="25" t="s">
-        <v>297</v>
+        <v>301</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="6"/>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35" s="24" t="s">
+        <v>302</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -5899,63 +5850,63 @@
       <c r="K35" s="13"/>
       <c r="L35" s="14"/>
     </row>
-    <row r="36" spans="1:12" ht="19.95" customHeight="1">
+    <row r="36" spans="1:12">
       <c r="A36" s="15"/>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="6"/>
-      <c r="J36" s="6"/>
-      <c r="K36" s="6"/>
+      <c r="B36" s="10"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="10"/>
+      <c r="I36" s="10"/>
+      <c r="J36" s="10"/>
+      <c r="K36" s="10"/>
       <c r="L36" s="16"/>
     </row>
-    <row r="37" spans="1:12" ht="19.95" customHeight="1">
+    <row r="37" spans="1:12">
       <c r="A37" s="15"/>
-      <c r="B37" s="6"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6"/>
-      <c r="J37" s="6"/>
-      <c r="K37" s="6"/>
+      <c r="B37" s="10"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="10"/>
+      <c r="I37" s="10"/>
+      <c r="J37" s="10"/>
+      <c r="K37" s="10"/>
       <c r="L37" s="16"/>
     </row>
-    <row r="38" spans="1:12" ht="19.95" customHeight="1">
+    <row r="38" spans="1:12">
       <c r="A38" s="15"/>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="6"/>
-      <c r="K38" s="6"/>
+      <c r="B38" s="10"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="10"/>
+      <c r="G38" s="10"/>
+      <c r="H38" s="10"/>
+      <c r="I38" s="10"/>
+      <c r="J38" s="10"/>
+      <c r="K38" s="10"/>
       <c r="L38" s="16"/>
     </row>
-    <row r="39" spans="1:12" ht="19.95" customHeight="1">
+    <row r="39" spans="1:12">
       <c r="A39" s="15"/>
-      <c r="B39" s="6"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="6"/>
-      <c r="K39" s="6"/>
+      <c r="B39" s="10"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="10"/>
+      <c r="F39" s="10"/>
+      <c r="G39" s="10"/>
+      <c r="H39" s="10"/>
+      <c r="I39" s="10"/>
+      <c r="J39" s="10"/>
+      <c r="K39" s="10"/>
       <c r="L39" s="16"/>
     </row>
-    <row r="40" spans="1:12" ht="19.95" customHeight="1">
+    <row r="40" spans="1:12">
       <c r="A40" s="17"/>
       <c r="B40" s="18"/>
       <c r="C40" s="18"/>
@@ -5969,58 +5920,52 @@
       <c r="K40" s="18"/>
       <c r="L40" s="19"/>
     </row>
-    <row r="41" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="42" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="43" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="44" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="45" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="46" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="47" spans="1:12" ht="24" customHeight="1">
-      <c r="A47" s="22" t="s">
-        <v>93</v>
-      </c>
-      <c r="B47" s="10"/>
-      <c r="C47" s="10"/>
-      <c r="D47" s="10"/>
-      <c r="E47" s="10"/>
-      <c r="F47" s="10"/>
-      <c r="G47" s="10"/>
-      <c r="H47" s="10"/>
-      <c r="I47" s="10"/>
-      <c r="J47" s="10"/>
-      <c r="K47" s="10"/>
-      <c r="L47" s="8"/>
-    </row>
-    <row r="48" spans="1:12" ht="19.95" customHeight="1">
+    <row r="47" spans="1:12">
+      <c r="A47" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="8"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="8"/>
+      <c r="I47" s="8"/>
+      <c r="J47" s="8"/>
+      <c r="K47" s="8"/>
+      <c r="L47" s="6"/>
+    </row>
+    <row r="48" spans="1:12" ht="16.2">
       <c r="A48" s="4" t="s">
         <v>48</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="F48" s="24"/>
-      <c r="G48" s="10"/>
-      <c r="H48" s="10"/>
-      <c r="I48" s="10"/>
-      <c r="J48" s="10"/>
-      <c r="K48" s="10"/>
-      <c r="L48" s="8"/>
-    </row>
-    <row r="49" spans="1:12" ht="19.95" customHeight="1">
+        <v>98</v>
+      </c>
+      <c r="F48" s="22"/>
+      <c r="G48" s="8"/>
+      <c r="H48" s="8"/>
+      <c r="I48" s="8"/>
+      <c r="J48" s="8"/>
+      <c r="K48" s="8"/>
+      <c r="L48" s="6"/>
+    </row>
+    <row r="49" spans="1:12" ht="16.2">
       <c r="A49" s="1">
         <v>1</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>79</v>
@@ -6029,22 +5974,22 @@
         <v>79</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="F49" s="12"/>
-      <c r="G49" s="10"/>
-      <c r="H49" s="10"/>
-      <c r="I49" s="10"/>
-      <c r="J49" s="10"/>
-      <c r="K49" s="10"/>
-      <c r="L49" s="8"/>
-    </row>
-    <row r="50" spans="1:12" ht="19.95" customHeight="1">
+      <c r="G49" s="8"/>
+      <c r="H49" s="8"/>
+      <c r="I49" s="8"/>
+      <c r="J49" s="8"/>
+      <c r="K49" s="8"/>
+      <c r="L49" s="6"/>
+    </row>
+    <row r="50" spans="1:12" ht="16.2">
       <c r="A50" s="1">
         <v>2</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>79</v>
@@ -6053,22 +5998,22 @@
         <v>79</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="F50" s="12"/>
-      <c r="G50" s="10"/>
-      <c r="H50" s="10"/>
-      <c r="I50" s="10"/>
-      <c r="J50" s="10"/>
-      <c r="K50" s="10"/>
-      <c r="L50" s="8"/>
-    </row>
-    <row r="51" spans="1:12" ht="19.95" customHeight="1">
+      <c r="G50" s="8"/>
+      <c r="H50" s="8"/>
+      <c r="I50" s="8"/>
+      <c r="J50" s="8"/>
+      <c r="K50" s="8"/>
+      <c r="L50" s="6"/>
+    </row>
+    <row r="51" spans="1:12" ht="16.2">
       <c r="A51" s="1">
         <v>3</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>79</v>
@@ -6077,147 +6022,130 @@
         <v>79</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="F51" s="12"/>
-      <c r="G51" s="10"/>
-      <c r="H51" s="10"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="10"/>
-      <c r="K51" s="10"/>
-      <c r="L51" s="8"/>
-    </row>
-    <row r="52" spans="1:12" ht="19.95" customHeight="1">
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="6"/>
+    </row>
+    <row r="52" spans="1:12" ht="16.2">
       <c r="A52" s="1">
         <v>4</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="F52" s="12"/>
-      <c r="G52" s="10"/>
-      <c r="H52" s="10"/>
-      <c r="I52" s="10"/>
-      <c r="J52" s="10"/>
-      <c r="K52" s="10"/>
-      <c r="L52" s="8"/>
-    </row>
-    <row r="53" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="54" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="55" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="56" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="57" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="58" spans="1:12" ht="19.95" customHeight="1"/>
-    <row r="59" spans="1:12" ht="24" customHeight="1">
-      <c r="A59" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="B59" s="10"/>
-      <c r="C59" s="10"/>
-      <c r="D59" s="10"/>
-      <c r="E59" s="10"/>
-      <c r="F59" s="10"/>
-      <c r="G59" s="10"/>
-      <c r="H59" s="10"/>
-      <c r="I59" s="10"/>
-      <c r="J59" s="10"/>
-      <c r="K59" s="10"/>
-      <c r="L59" s="8"/>
-    </row>
-    <row r="60" spans="1:12" ht="19.95" customHeight="1">
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="8"/>
+      <c r="J52" s="8"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="6"/>
+    </row>
+    <row r="59" spans="1:12">
+      <c r="A59" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="B59" s="8"/>
+      <c r="C59" s="8"/>
+      <c r="D59" s="8"/>
+      <c r="E59" s="8"/>
+      <c r="F59" s="8"/>
+      <c r="G59" s="8"/>
+      <c r="H59" s="8"/>
+      <c r="I59" s="8"/>
+      <c r="J59" s="8"/>
+      <c r="K59" s="8"/>
+      <c r="L59" s="6"/>
+    </row>
+    <row r="60" spans="1:12" ht="16.2">
       <c r="A60" s="4" t="s">
         <v>48</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E60" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F60" s="24"/>
-      <c r="G60" s="10"/>
-      <c r="H60" s="10"/>
-      <c r="I60" s="10"/>
-      <c r="J60" s="10"/>
-      <c r="K60" s="10"/>
-      <c r="L60" s="8"/>
-    </row>
-    <row r="61" spans="1:12" ht="19.95" customHeight="1">
+      <c r="F60" s="22"/>
+      <c r="G60" s="8"/>
+      <c r="H60" s="8"/>
+      <c r="I60" s="8"/>
+      <c r="J60" s="8"/>
+      <c r="K60" s="8"/>
+      <c r="L60" s="6"/>
+    </row>
+    <row r="61" spans="1:12" ht="16.2">
       <c r="A61" s="1">
         <v>1</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="F61" s="12"/>
-      <c r="G61" s="10"/>
-      <c r="H61" s="10"/>
-      <c r="I61" s="10"/>
-      <c r="J61" s="10"/>
-      <c r="K61" s="10"/>
-      <c r="L61" s="8"/>
-    </row>
-    <row r="62" spans="1:12" ht="19.95" customHeight="1">
+      <c r="G61" s="8"/>
+      <c r="H61" s="8"/>
+      <c r="I61" s="8"/>
+      <c r="J61" s="8"/>
+      <c r="K61" s="8"/>
+      <c r="L61" s="6"/>
+    </row>
+    <row r="62" spans="1:12" ht="16.2">
       <c r="A62" s="1">
         <v>2</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="F62" s="12"/>
-      <c r="G62" s="10"/>
-      <c r="H62" s="10"/>
-      <c r="I62" s="10"/>
-      <c r="J62" s="10"/>
-      <c r="K62" s="10"/>
-      <c r="L62" s="8"/>
+      <c r="G62" s="8"/>
+      <c r="H62" s="8"/>
+      <c r="I62" s="8"/>
+      <c r="J62" s="8"/>
+      <c r="K62" s="8"/>
+      <c r="L62" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="G6:L6"/>
-    <mergeCell ref="F61:L61"/>
-    <mergeCell ref="F48:L48"/>
-    <mergeCell ref="A35:L40"/>
-    <mergeCell ref="F60:L60"/>
-    <mergeCell ref="F49:L49"/>
-    <mergeCell ref="F51:L51"/>
-    <mergeCell ref="A59:L59"/>
-    <mergeCell ref="F50:L50"/>
-    <mergeCell ref="F52:L52"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="G8:L8"/>
     <mergeCell ref="F62:L62"/>
@@ -6234,9 +6162,20 @@
     <mergeCell ref="A12:E20"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="A21:L21"/>
+    <mergeCell ref="A35:L40"/>
+    <mergeCell ref="F60:L60"/>
+    <mergeCell ref="F49:L49"/>
+    <mergeCell ref="F51:L51"/>
+    <mergeCell ref="A59:L59"/>
+    <mergeCell ref="F50:L50"/>
+    <mergeCell ref="F52:L52"/>
+    <mergeCell ref="G6:L6"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="F61:L61"/>
+    <mergeCell ref="F48:L48"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" scale="43" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="28" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>